--- a/apps/backend/internal/profile/templates/ipra-passenger-profile-template.xlsx
+++ b/apps/backend/internal/profile/templates/ipra-passenger-profile-template.xlsx
@@ -82,7 +82,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.00" customWidth="1"/>
@@ -106,202 +106,212 @@
     <col min="19" max="19" width="20.00" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基础画像模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">证件号码</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姓名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">证件类型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">签发地区</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">国籍</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">性别</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">出生日期</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">联系电话</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">订票编码</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">航班号</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">出发地</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">目的地</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">出行目的</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">近年出入境次数</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">职业</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">工作单位</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">风险标签</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">违法犯罪记录</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">E92834102</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">张伟</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">护照</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CN</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">中国</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">男</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1990-04-12</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">13800138000</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CX880-LAX</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">CX880</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">香港</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">洛杉矶</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">旅游</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">自由职业</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">无固定单位</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">异常行程,重点关注</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">无</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="S3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">示例数据，可删除</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
+  <autoFilter ref="A2:S2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>